--- a/docs/環境構築手順書.xlsx
+++ b/docs/環境構築手順書.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="715">
   <si>
     <t>良い構成だと思います。</t>
   </si>
@@ -2741,6 +2741,143 @@
   </si>
   <si>
     <t>今回の3人・月6時間程度の学習規模なら、まずはこの「Hello Flutter!」疎通確認を完成させるのが最初のマイルストーンになります。</t>
+  </si>
+  <si>
+    <t>動作確認等はブラウザのスマホ表示等で確認しようと思ってるんだけどそれじゃ無理？ エミュレーターとか使う想定なので、Android SDKとVisual Studioは入れてなかった。</t>
+  </si>
+  <si>
+    <r>
+      <t>その考え方は</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>かなり合理的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+  </si>
+  <si>
+    <t>結論から言うと、</t>
+  </si>
+  <si>
+    <t>Web（Chrome）で動作確認するなら、Android SDKは必須ではありません。</t>
+  </si>
+  <si>
+    <t>Visual Studioも不要です。</t>
+  </si>
+  <si>
+    <t>ただし、チャットアプリとして完成させることを考えると、途中でAndroid実機またはエミュレーターでの確認は一度はした方がいいです。</t>
+  </si>
+  <si>
+    <t>Flutterには3つの実行先があります</t>
+  </si>
+  <si>
+    <t>├── Web（Chrome）</t>
+  </si>
+  <si>
+    <t>├── Android</t>
+  </si>
+  <si>
+    <t>├── iOS（Macのみ）</t>
+  </si>
+  <si>
+    <t>あなたの場合、今は</t>
+  </si>
+  <si>
+    <t>✅ Chrome</t>
+  </si>
+  <si>
+    <t>なので、</t>
+  </si>
+  <si>
+    <t>flutter run -d chrome</t>
+  </si>
+  <si>
+    <t>でFlutterアプリを起動できます。</t>
+  </si>
+  <si>
+    <t>つまり、</t>
+  </si>
+  <si>
+    <t>Flutter(Web)</t>
+  </si>
+  <si>
+    <r>
+      <t>という通信確認は</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Android SDKなしでもできます。</t>
+    </r>
+  </si>
+  <si>
+    <t>今回のチャットアプリなら</t>
+  </si>
+  <si>
+    <t>開発初期は</t>
+  </si>
+  <si>
+    <t>まで十分開発できます。</t>
+  </si>
+  <si>
+    <t>Android SDKが必要になるタイミング</t>
+  </si>
+  <si>
+    <t>Android通知</t>
+  </si>
+  <si>
+    <t>カメラ</t>
+  </si>
+  <si>
+    <t>GPS</t>
+  </si>
+  <si>
+    <t>ファイル保存</t>
+  </si>
+  <si>
+    <t>Play Storeへ公開</t>
+  </si>
+  <si>
+    <t>実機でレイアウト確認</t>
+  </si>
+  <si>
+    <t>この辺りになると必要になります。</t>
+  </si>
+  <si>
+    <t>チャットアプリでも</t>
+  </si>
+  <si>
+    <t>プッシュ通知</t>
+  </si>
+  <si>
+    <t>カメラで画像送信</t>
+  </si>
+  <si>
+    <t>を作るなら、最終的にはAndroid環境が必要です。</t>
   </si>
 </sst>
 </file>
@@ -2985,7 +3122,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3093,6 +3230,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8224,7 +8364,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I336"/>
+  <dimension ref="B2:AH336"/>
   <sheetFormatPr defaultColWidth="3.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="3.77734375" style="23"/>
@@ -9334,574 +9474,758 @@
       <c r="C208" s="33"/>
       <c r="D208" s="33"/>
     </row>
-    <row r="209" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B209" s="33"/>
       <c r="C209" s="33"/>
       <c r="D209" s="33"/>
     </row>
-    <row r="210" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B210" s="33"/>
       <c r="C210" s="33"/>
       <c r="D210" s="33"/>
     </row>
-    <row r="211" spans="2:4" ht="28.2" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:34" ht="28.2" x14ac:dyDescent="0.2">
       <c r="B211" s="12" t="s">
         <v>447</v>
       </c>
       <c r="C211" s="33"/>
       <c r="D211" s="33"/>
-    </row>
-    <row r="212" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH211" s="10" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="212" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B212" s="33"/>
       <c r="C212" s="33"/>
       <c r="D212" s="33"/>
-    </row>
-    <row r="213" spans="2:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="AH212" s="10"/>
+    </row>
+    <row r="213" spans="2:34" ht="21" x14ac:dyDescent="0.2">
       <c r="B213" s="11" t="s">
         <v>448</v>
       </c>
       <c r="C213" s="33"/>
       <c r="D213" s="33"/>
-    </row>
-    <row r="214" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH213" s="10" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="214" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B214" s="33"/>
       <c r="C214" s="33"/>
       <c r="D214" s="33"/>
-    </row>
-    <row r="215" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH214" s="10" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="215" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B215" s="33" t="s">
         <v>449</v>
       </c>
       <c r="C215" s="33"/>
       <c r="D215" s="33"/>
-    </row>
-    <row r="216" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH215" s="13"/>
+    </row>
+    <row r="216" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B216" s="33"/>
       <c r="C216" s="33"/>
       <c r="D216" s="33"/>
-    </row>
-    <row r="217" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH216" s="52" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="217" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B217" s="37" t="s">
         <v>450</v>
       </c>
       <c r="C217" s="33"/>
       <c r="D217" s="33"/>
-    </row>
-    <row r="218" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH217" s="52" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="218" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B218" s="33"/>
       <c r="C218" s="33"/>
       <c r="D218" s="33"/>
-    </row>
-    <row r="219" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH218" s="10"/>
+    </row>
+    <row r="219" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B219" s="33" t="s">
         <v>451</v>
       </c>
       <c r="C219" s="33"/>
       <c r="D219" s="33"/>
-    </row>
-    <row r="220" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH219" s="10" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="220" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B220" s="33"/>
       <c r="C220" s="33"/>
       <c r="D220" s="33"/>
-    </row>
-    <row r="221" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH220" s="10"/>
+    </row>
+    <row r="221" spans="2:34" ht="21" x14ac:dyDescent="0.2">
       <c r="B221" s="33"/>
       <c r="C221" s="33"/>
       <c r="D221" s="33"/>
-    </row>
-    <row r="222" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH221" s="11" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="222" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B222" s="33"/>
       <c r="C222" s="33"/>
       <c r="D222" s="33"/>
-    </row>
-    <row r="223" spans="2:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="AH222" s="15"/>
+    </row>
+    <row r="223" spans="2:34" ht="21" x14ac:dyDescent="0.2">
       <c r="B223" s="11" t="s">
         <v>452</v>
       </c>
       <c r="C223" s="33"/>
       <c r="D223" s="33"/>
-    </row>
-    <row r="224" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH223" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="224" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B224" s="33"/>
       <c r="C224" s="33"/>
       <c r="D224" s="33"/>
-    </row>
-    <row r="225" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH224" s="14" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="225" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B225" s="33" t="s">
         <v>453</v>
       </c>
       <c r="C225" s="33"/>
       <c r="D225" s="33"/>
-    </row>
-    <row r="226" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH225" s="14" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="226" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B226" s="33"/>
       <c r="C226" s="33"/>
       <c r="D226" s="33"/>
-    </row>
-    <row r="227" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH226" s="14" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="227" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B227" s="33" t="s">
         <v>454</v>
       </c>
       <c r="C227" s="33"/>
       <c r="D227" s="33"/>
-    </row>
-    <row r="228" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH227" s="10"/>
+    </row>
+    <row r="228" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B228" s="33"/>
       <c r="C228" s="33"/>
       <c r="D228" s="33"/>
-    </row>
-    <row r="229" spans="2:4" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="AH228" s="10" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="229" spans="2:34" ht="16.2" x14ac:dyDescent="0.2">
       <c r="B229" s="24" t="s">
         <v>455</v>
       </c>
       <c r="C229" s="33"/>
       <c r="D229" s="33"/>
-    </row>
-    <row r="230" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH229" s="15"/>
+    </row>
+    <row r="230" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B230" s="33"/>
       <c r="C230" s="33"/>
       <c r="D230" s="33"/>
-    </row>
-    <row r="231" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH230" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="231" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B231" s="33" t="s">
         <v>456</v>
       </c>
       <c r="C231" s="33"/>
       <c r="D231" s="33"/>
-    </row>
-    <row r="232" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH231" s="15"/>
+    </row>
+    <row r="232" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B232" s="33"/>
       <c r="C232" s="33"/>
       <c r="D232" s="33"/>
-    </row>
-    <row r="233" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="AH232" s="14" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="233" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B233" s="36" t="s">
         <v>457</v>
       </c>
       <c r="C233" s="33"/>
       <c r="D233" s="33"/>
-    </row>
-    <row r="234" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH233" s="10"/>
+    </row>
+    <row r="234" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B234" s="33"/>
       <c r="C234" s="33"/>
       <c r="D234" s="33"/>
-    </row>
-    <row r="235" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH234" s="10" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="235" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B235" s="33" t="s">
         <v>458</v>
       </c>
       <c r="C235" s="33"/>
       <c r="D235" s="33"/>
-    </row>
-    <row r="236" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH235" s="15"/>
+    </row>
+    <row r="236" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B236" s="33"/>
       <c r="C236" s="33"/>
       <c r="D236" s="33"/>
-    </row>
-    <row r="237" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH236" s="14" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="237" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B237" s="33"/>
       <c r="C237" s="33"/>
       <c r="D237" s="33"/>
-    </row>
-    <row r="238" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH237" s="10"/>
+    </row>
+    <row r="238" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B238" s="33"/>
       <c r="C238" s="33"/>
       <c r="D238" s="33"/>
-    </row>
-    <row r="239" spans="2:4" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="AH238" s="10" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="239" spans="2:34" ht="16.2" x14ac:dyDescent="0.2">
       <c r="B239" s="24" t="s">
         <v>459</v>
       </c>
       <c r="C239" s="33"/>
       <c r="D239" s="33"/>
-    </row>
-    <row r="240" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH239" s="10"/>
+    </row>
+    <row r="240" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B240" s="33"/>
       <c r="C240" s="33"/>
       <c r="D240" s="33"/>
-    </row>
-    <row r="241" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH240" s="10" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="241" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B241" s="33" t="s">
         <v>460</v>
       </c>
       <c r="C241" s="33"/>
       <c r="D241" s="33"/>
-    </row>
-    <row r="242" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH241" s="15"/>
+    </row>
+    <row r="242" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B242" s="33"/>
       <c r="C242" s="33"/>
       <c r="D242" s="33"/>
-    </row>
-    <row r="243" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH242" s="14" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="243" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B243" s="33" t="s">
         <v>461</v>
       </c>
       <c r="C243" s="33"/>
       <c r="D243" s="33"/>
-    </row>
-    <row r="244" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH243" s="14" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="244" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B244" s="33" t="s">
         <v>462</v>
       </c>
       <c r="C244" s="33"/>
       <c r="D244" s="33"/>
-    </row>
-    <row r="245" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH244" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="245" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B245" s="33" t="s">
         <v>463</v>
       </c>
       <c r="C245" s="33"/>
       <c r="D245" s="33"/>
-    </row>
-    <row r="246" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH245" s="14" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="246" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B246" s="33"/>
       <c r="C246" s="33"/>
       <c r="D246" s="33"/>
-    </row>
-    <row r="247" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH246" s="14" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="247" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B247" s="33"/>
       <c r="C247" s="33"/>
       <c r="D247" s="33"/>
-    </row>
-    <row r="248" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH247" s="10"/>
+    </row>
+    <row r="248" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B248" s="33"/>
       <c r="C248" s="33"/>
       <c r="D248" s="33"/>
-    </row>
-    <row r="249" spans="2:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="AH248" s="10" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="249" spans="2:34" ht="21" x14ac:dyDescent="0.2">
       <c r="B249" s="11" t="s">
         <v>464</v>
       </c>
       <c r="C249" s="33"/>
       <c r="D249" s="33"/>
-    </row>
-    <row r="250" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH249" s="10"/>
+    </row>
+    <row r="250" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B250" s="33"/>
       <c r="C250" s="33"/>
       <c r="D250" s="33"/>
-    </row>
-    <row r="251" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH250" s="10"/>
+    </row>
+    <row r="251" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B251" s="33" t="s">
         <v>465</v>
       </c>
       <c r="C251" s="33"/>
       <c r="D251" s="33"/>
-    </row>
-    <row r="252" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH251" s="10"/>
+    </row>
+    <row r="252" spans="2:34" ht="21" x14ac:dyDescent="0.2">
       <c r="B252" s="33"/>
       <c r="C252" s="33"/>
       <c r="D252" s="33"/>
-    </row>
-    <row r="253" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="AH252" s="11" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="253" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B253" s="36" t="s">
         <v>466</v>
       </c>
       <c r="C253" s="33"/>
       <c r="D253" s="33"/>
-    </row>
-    <row r="254" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH253" s="10"/>
+    </row>
+    <row r="254" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B254" s="33"/>
       <c r="C254" s="33"/>
       <c r="D254" s="33"/>
-    </row>
-    <row r="255" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH254" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="255" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B255" s="33" t="s">
         <v>467</v>
       </c>
       <c r="C255" s="33"/>
       <c r="D255" s="33"/>
-    </row>
-    <row r="256" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH255" s="15"/>
+    </row>
+    <row r="256" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B256" s="33"/>
       <c r="C256" s="33"/>
       <c r="D256" s="33"/>
-    </row>
-    <row r="257" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="AH256" s="14" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="257" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B257" s="36" t="s">
         <v>468</v>
       </c>
       <c r="C257" s="33"/>
       <c r="D257" s="33"/>
-    </row>
-    <row r="258" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH257" s="14" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="258" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B258" s="33"/>
       <c r="C258" s="33"/>
       <c r="D258" s="33"/>
-    </row>
-    <row r="259" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH258" s="14" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="259" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B259" s="33" t="s">
         <v>469</v>
       </c>
       <c r="C259" s="33"/>
       <c r="D259" s="33"/>
-    </row>
-    <row r="260" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH259" s="14" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="260" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B260" s="33"/>
       <c r="C260" s="33"/>
       <c r="D260" s="33"/>
-    </row>
-    <row r="261" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH260" s="14" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="261" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B261" s="33"/>
       <c r="C261" s="33"/>
       <c r="D261" s="33"/>
-    </row>
-    <row r="262" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH261" s="10"/>
+    </row>
+    <row r="262" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B262" s="33"/>
       <c r="C262" s="33"/>
       <c r="D262" s="33"/>
-    </row>
-    <row r="263" spans="2:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="AH262" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="263" spans="2:34" ht="21" x14ac:dyDescent="0.2">
       <c r="B263" s="11" t="s">
         <v>470</v>
       </c>
       <c r="C263" s="33"/>
       <c r="D263" s="33"/>
-    </row>
-    <row r="264" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH263" s="15"/>
+    </row>
+    <row r="264" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B264" s="33"/>
       <c r="C264" s="33"/>
       <c r="D264" s="33"/>
-    </row>
-    <row r="265" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH264" s="14" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="265" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B265" s="33" t="s">
         <v>471</v>
       </c>
       <c r="C265" s="33"/>
       <c r="D265" s="33"/>
-    </row>
-    <row r="266" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH265" s="14" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="266" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B266" s="33"/>
       <c r="C266" s="33"/>
       <c r="D266" s="33"/>
-    </row>
-    <row r="267" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH266" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="267" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B267" s="33" t="s">
         <v>472</v>
       </c>
       <c r="C267" s="33"/>
       <c r="D267" s="33"/>
-    </row>
-    <row r="268" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH267" s="14" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="268" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B268" s="33"/>
       <c r="C268" s="33"/>
       <c r="D268" s="33"/>
-    </row>
-    <row r="269" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="AH268" s="14" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="269" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B269" s="36" t="s">
         <v>473</v>
       </c>
       <c r="C269" s="33"/>
       <c r="D269" s="33"/>
-    </row>
-    <row r="270" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="AH269" s="10"/>
+    </row>
+    <row r="270" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B270" s="36" t="s">
         <v>474</v>
       </c>
       <c r="C270" s="33"/>
       <c r="D270" s="33"/>
-    </row>
-    <row r="271" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="AH270" s="10" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="271" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B271" s="36" t="s">
         <v>191</v>
       </c>
       <c r="C271" s="33"/>
       <c r="D271" s="33"/>
-    </row>
-    <row r="272" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="AH271" s="10"/>
+    </row>
+    <row r="272" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B272" s="36" t="s">
         <v>474</v>
       </c>
       <c r="C272" s="33"/>
       <c r="D272" s="33"/>
-    </row>
-    <row r="273" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="AH272" s="10"/>
+    </row>
+    <row r="273" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B273" s="36" t="s">
         <v>475</v>
       </c>
       <c r="C273" s="33"/>
       <c r="D273" s="33"/>
-    </row>
-    <row r="274" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="AH273" s="10"/>
+    </row>
+    <row r="274" spans="2:34" ht="21" x14ac:dyDescent="0.2">
       <c r="B274" s="36" t="s">
         <v>474</v>
       </c>
       <c r="C274" s="33"/>
       <c r="D274" s="33"/>
-    </row>
-    <row r="275" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="AH274" s="11" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="275" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B275" s="36" t="s">
         <v>26</v>
       </c>
       <c r="C275" s="33"/>
       <c r="D275" s="33"/>
-    </row>
-    <row r="276" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH275" s="10"/>
+    </row>
+    <row r="276" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B276" s="33"/>
       <c r="C276" s="33"/>
       <c r="D276" s="33"/>
-    </row>
-    <row r="277" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH276" s="10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="277" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B277" s="33" t="s">
         <v>476</v>
       </c>
       <c r="C277" s="33"/>
       <c r="D277" s="33"/>
-    </row>
-    <row r="278" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH277" s="13"/>
+    </row>
+    <row r="278" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B278" s="33"/>
       <c r="C278" s="33"/>
       <c r="D278" s="33"/>
-    </row>
-    <row r="279" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH278" s="13" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="279" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B279" s="33" t="s">
         <v>477</v>
       </c>
       <c r="C279" s="33"/>
       <c r="D279" s="33"/>
-    </row>
-    <row r="280" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH279" s="13" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="280" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B280" s="33"/>
       <c r="C280" s="33"/>
       <c r="D280" s="33"/>
-    </row>
-    <row r="281" spans="2:4" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="AH280" s="13" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="281" spans="2:34" ht="16.2" x14ac:dyDescent="0.2">
       <c r="B281" s="24" t="s">
         <v>478</v>
       </c>
       <c r="C281" s="33"/>
       <c r="D281" s="33"/>
-    </row>
-    <row r="282" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH281" s="13" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="282" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B282" s="33"/>
       <c r="C282" s="33"/>
       <c r="D282" s="33"/>
-    </row>
-    <row r="283" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH282" s="13" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="283" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B283" s="33" t="s">
         <v>126</v>
       </c>
       <c r="C283" s="33"/>
       <c r="D283" s="33"/>
-    </row>
-    <row r="284" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH283" s="13" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="284" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B284" s="33"/>
       <c r="C284" s="33"/>
       <c r="D284" s="33"/>
-    </row>
-    <row r="285" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="AH284" s="10"/>
+    </row>
+    <row r="285" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B285" s="36" t="s">
         <v>479</v>
       </c>
       <c r="C285" s="33"/>
       <c r="D285" s="33"/>
-    </row>
-    <row r="286" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH285" s="10" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="286" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B286" s="33"/>
       <c r="C286" s="33"/>
       <c r="D286" s="33"/>
-    </row>
-    <row r="287" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH286" s="10"/>
+    </row>
+    <row r="287" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B287" s="33" t="s">
         <v>480</v>
       </c>
       <c r="C287" s="33"/>
       <c r="D287" s="33"/>
-    </row>
-    <row r="288" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH287" s="10" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="288" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B288" s="33"/>
       <c r="C288" s="33"/>
       <c r="D288" s="33"/>
-    </row>
-    <row r="289" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="AH288" s="13"/>
+    </row>
+    <row r="289" spans="2:34" ht="15" x14ac:dyDescent="0.2">
       <c r="B289" s="36" t="s">
         <v>481</v>
       </c>
       <c r="C289" s="33"/>
       <c r="D289" s="33"/>
-    </row>
-    <row r="290" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH289" s="13" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="290" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B290" s="33"/>
       <c r="C290" s="33"/>
       <c r="D290" s="33"/>
-    </row>
-    <row r="291" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH290" s="13" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="291" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B291" s="33"/>
       <c r="C291" s="33"/>
       <c r="D291" s="33"/>
-    </row>
-    <row r="292" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="AH291" s="10"/>
+    </row>
+    <row r="292" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B292" s="33"/>
       <c r="C292" s="33"/>
       <c r="D292" s="33"/>
-    </row>
-    <row r="293" spans="2:4" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="AH292" s="10" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="293" spans="2:34" ht="16.2" x14ac:dyDescent="0.2">
       <c r="B293" s="24" t="s">
         <v>482</v>
       </c>
       <c r="C293" s="33"/>
       <c r="D293" s="33"/>
     </row>
-    <row r="294" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="294" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B294" s="33"/>
       <c r="C294" s="33"/>
       <c r="D294" s="33"/>
     </row>
-    <row r="295" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="295" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B295" s="33" t="s">
         <v>483</v>
       </c>
       <c r="C295" s="33"/>
       <c r="D295" s="33"/>
     </row>
-    <row r="296" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="296" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B296" s="33"/>
       <c r="C296" s="33"/>
       <c r="D296" s="33"/>
     </row>
-    <row r="297" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="297" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B297" s="33" t="s">
         <v>484</v>
       </c>
       <c r="C297" s="33"/>
       <c r="D297" s="33"/>
     </row>
-    <row r="298" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="298" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B298" s="33" t="s">
         <v>485</v>
       </c>
       <c r="C298" s="33"/>
       <c r="D298" s="33"/>
     </row>
-    <row r="299" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="299" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B299" s="33" t="s">
         <v>486</v>
       </c>
       <c r="C299" s="33"/>
       <c r="D299" s="33"/>
     </row>
-    <row r="300" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="300" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B300" s="33" t="s">
         <v>487</v>
       </c>
       <c r="C300" s="33"/>
       <c r="D300" s="33"/>
     </row>
-    <row r="301" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="301" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B301" s="33"/>
       <c r="C301" s="33"/>
       <c r="D301" s="33"/>
     </row>
-    <row r="302" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="302" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B302" s="33"/>
       <c r="C302" s="33"/>
       <c r="D302" s="33"/>
     </row>
-    <row r="303" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="303" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B303" s="33"/>
       <c r="C303" s="33"/>
       <c r="D303" s="33"/>
     </row>
-    <row r="304" spans="2:4" ht="21" x14ac:dyDescent="0.2">
+    <row r="304" spans="2:34" ht="21" x14ac:dyDescent="0.2">
       <c r="B304" s="11" t="s">
         <v>488</v>
       </c>
